--- a/ARM Functions/Item Edits/Mega Stone Emergency Exit.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Emergency Exit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE06BF0F-0419-480D-92F9-F0463D1915BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F4927-B8C1-4D3D-A330-DBCE4B9896B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Code" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="188">
   <si>
     <t>mov r0, r5</t>
   </si>
@@ -117,57 +117,15 @@
     <t>bl 0x00092298</t>
   </si>
   <si>
-    <t>ldrh r0, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>BC00D0E1</t>
-  </si>
-  <si>
     <t>get pointer</t>
   </si>
   <si>
-    <t>get species</t>
-  </si>
-  <si>
-    <t>get table</t>
-  </si>
-  <si>
-    <t>0020A0E3</t>
-  </si>
-  <si>
-    <t>mov r2, 0x0</t>
-  </si>
-  <si>
-    <t>B23091E1</t>
-  </si>
-  <si>
-    <t>ldrh r3, [r1, r2]</t>
-  </si>
-  <si>
-    <t>030050E1</t>
-  </si>
-  <si>
-    <t>cmp r0, r3</t>
-  </si>
-  <si>
-    <t>0300000A</t>
-  </si>
-  <si>
     <t>000050E3</t>
   </si>
   <si>
     <t>cmp r0, 0x0</t>
   </si>
   <si>
-    <t>022082E2</t>
-  </si>
-  <si>
-    <t>add r2, r2, 0x2</t>
-  </si>
-  <si>
-    <t>F8FFFFEA</t>
-  </si>
-  <si>
     <t>Table</t>
   </si>
   <si>
@@ -585,79 +543,85 @@
     <t>29B5FEEB</t>
   </si>
   <si>
-    <t>5B00001A</t>
-  </si>
-  <si>
     <t>F4DEFEEB</t>
   </si>
   <si>
-    <t>60119FE5</t>
-  </si>
-  <si>
-    <t>5000000A</t>
-  </si>
-  <si>
-    <t>7CE4FEEB</t>
-  </si>
-  <si>
     <t>4A00001A</t>
   </si>
   <si>
-    <t>C7DFFEEB</t>
-  </si>
-  <si>
-    <t>C3DFFEEB</t>
-  </si>
-  <si>
     <t>4100008A</t>
   </si>
   <si>
-    <t>A394FEEB</t>
-  </si>
-  <si>
-    <t>87C3FEEB</t>
-  </si>
-  <si>
-    <t>E7B3FEEB</t>
-  </si>
-  <si>
-    <t>5E89FEEB</t>
-  </si>
-  <si>
-    <t>DBB3FEEB</t>
-  </si>
-  <si>
     <t>B429DFE1</t>
   </si>
   <si>
-    <t>32BDFEEB</t>
-  </si>
-  <si>
-    <t>1594FEEB</t>
-  </si>
-  <si>
-    <t>1294FEEB</t>
-  </si>
-  <si>
-    <t>4B89FEEB</t>
-  </si>
-  <si>
-    <t>C8B3FEEB</t>
-  </si>
-  <si>
-    <t>AEE0FEEB</t>
-  </si>
-  <si>
-    <t>3289FEEA</t>
-  </si>
-  <si>
     <t>Mega Stone Emergency Exit 0x8F</t>
   </si>
   <si>
-    <t>Altaria</t>
-  </si>
-  <si>
-    <t>Ampharos</t>
+    <t>check Mega</t>
+  </si>
+  <si>
+    <t>bl 0x000D6F98</t>
+  </si>
+  <si>
+    <t>cmp r0, 0x1</t>
+  </si>
+  <si>
+    <t>5400001A</t>
+  </si>
+  <si>
+    <t>33F2FFEB</t>
+  </si>
+  <si>
+    <t>010050E3</t>
+  </si>
+  <si>
+    <t>4E00001A</t>
+  </si>
+  <si>
+    <t>83E4FEEB</t>
+  </si>
+  <si>
+    <t>CEDFFEEB</t>
+  </si>
+  <si>
+    <t>CADFFEEB</t>
+  </si>
+  <si>
+    <t>AA94FEEB</t>
+  </si>
+  <si>
+    <t>8EC3FEEB</t>
+  </si>
+  <si>
+    <t>EEB3FEEB</t>
+  </si>
+  <si>
+    <t>6589FEEB</t>
+  </si>
+  <si>
+    <t>E2B3FEEB</t>
+  </si>
+  <si>
+    <t>39BDFEEB</t>
+  </si>
+  <si>
+    <t>1C94FEEB</t>
+  </si>
+  <si>
+    <t>1994FEEB</t>
+  </si>
+  <si>
+    <t>5289FEEB</t>
+  </si>
+  <si>
+    <t>CFB3FEEB</t>
+  </si>
+  <si>
+    <t>B5E0FEEB</t>
+  </si>
+  <si>
+    <t>3989FEEA</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1198,7 +1162,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
@@ -1263,30 +1227,30 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="str">
-        <f t="shared" ref="A11:A80" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
+        <f t="shared" ref="A11:A74" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
         <v>000DA69C</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1295,10 +1259,10 @@
         <v>000DA6A0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1307,10 +1271,10 @@
         <v>000DA6A4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1319,13 +1283,13 @@
         <v>000DA6A8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1334,7 +1298,7 @@
         <v>000DA6AC</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>17</v>
@@ -1347,10 +1311,10 @@
         <v>000DA6B0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -1360,11 +1324,11 @@
         <v>000DA6B4</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C17" s="4" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A110)</f>
-        <v>bne 0x000DA828</v>
+        <f>_xlfn.CONCAT("bne 0x",A103)</f>
+        <v>bne 0x000DA80C</v>
       </c>
       <c r="D17" s="4"/>
     </row>
@@ -1374,13 +1338,13 @@
         <v>000DA6B8</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1389,10 +1353,10 @@
         <v>000DA6BC</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D19" s="7"/>
     </row>
@@ -1402,7 +1366,7 @@
         <v>000DA6C0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>18</v>
@@ -1415,13 +1379,13 @@
         <v>000DA6C4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1429,15 +1393,11 @@
         <f t="shared" si="1"/>
         <v>000DA6C8</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C22" s="2" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A112)-HEX2DEC(A22)-8,"]")</f>
-        <v>ldr r1, [pc, #352]</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>23</v>
+      <c r="B22" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1446,422 +1406,429 @@
         <v>000DA6CC</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>172</v>
+      </c>
+      <c r="C23" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A103)</f>
+        <v>bne 0x000DA80C</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2" t="str">
+      <c r="A24" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DA6D0</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>27</v>
+      <c r="B24" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2" t="str">
+      <c r="A25" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DA6D4</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="B25" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2" t="str">
+      <c r="A26" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DA6D8</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A31)</f>
-        <v>beq 0x000DA6EC</v>
-      </c>
+      <c r="B26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="2" t="str">
+      <c r="A27" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DA6DC</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B27" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="8" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A103)</f>
+        <v>bne 0x000DA80C</v>
+      </c>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="2" t="str">
+      <c r="A28" s="10" t="str">
         <f t="shared" si="1"/>
         <v>000DA6E0</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA6E4</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA6E8</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA6EC</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="10"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA6F0</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA6F4</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="10"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA6F8</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA6FC</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA700</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="10" t="str">
+        <f>_xlfn.CONCAT("bhi 0x",A103)</f>
+        <v>bhi 0x000DA80C</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA704</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA708</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA70C</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA710</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA714</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA718</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="13"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA71C</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="13"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA720</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA724</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" s="15" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E45)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x0008B564</v>
+      </c>
+      <c r="D45" s="15"/>
+      <c r="E45" s="2">
+        <v>768564</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA728</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="15"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA72C</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA730</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="16"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA734</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="16"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA738</v>
+      </c>
+      <c r="B50" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A110)</f>
-        <v>beq 0x000DA828</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA6E4</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA6E8</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A24)</f>
-        <v>b 0x000DA6D0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA6EC</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA6F0</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA6F4</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="8"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA6F8</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C34" s="8" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A110)</f>
-        <v>bne 0x000DA828</v>
-      </c>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA6FC</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA700</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="10"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA704</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" s="10"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA708</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" s="10"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA70C</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="10"/>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA710</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="10"/>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA714</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA718</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA71C</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" s="10" t="str">
-        <f>_xlfn.CONCAT("bhi 0x",A110)</f>
-        <v>bhi 0x000DA828</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA720</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA724</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D45" s="12"/>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA728</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA72C</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" s="12"/>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA730</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" s="13" t="s">
+      <c r="C50" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D50" s="16"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA73C</v>
+      </c>
+      <c r="B51" s="16" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA734</v>
-      </c>
-      <c r="B49" s="13" t="s">
+      <c r="C51" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="D51" s="16"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA740</v>
+      </c>
+      <c r="B52" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D49" s="13"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA738</v>
-      </c>
-      <c r="B50" s="13" t="s">
+      <c r="C52" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="D52" s="16"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA744</v>
+      </c>
+      <c r="B53" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="13"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA73C</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="15" t="s">
+      <c r="C53" s="16" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA740</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="C52" s="15" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E52)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x0008B564</v>
-      </c>
-      <c r="D52" s="15"/>
-      <c r="E52" s="2">
-        <v>768564</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA744</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="15"/>
+      <c r="D53" s="16"/>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="16" t="str">
@@ -1869,14 +1836,12 @@
         <v>000DA748</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>98</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D54" s="16"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="16" t="str">
@@ -1884,10 +1849,10 @@
         <v>000DA74C</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D55" s="16"/>
     </row>
@@ -1897,10 +1862,10 @@
         <v>000DA750</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="D56" s="16"/>
     </row>
@@ -1910,10 +1875,10 @@
         <v>000DA754</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="D57" s="16"/>
     </row>
@@ -1923,431 +1888,433 @@
         <v>000DA758</v>
       </c>
       <c r="B58" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="16"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA75C</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA760</v>
+      </c>
+      <c r="B60" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C60" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="16"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA75C</v>
-      </c>
-      <c r="B59" s="16" t="s">
+      <c r="D60" s="17"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA764</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D61" s="17"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA768</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" s="17" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E62)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x000876F8</v>
+      </c>
+      <c r="D62" s="17"/>
+      <c r="E62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C59" s="16" t="s">
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA76C</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="17"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA770</v>
+      </c>
+      <c r="B64" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D59" s="16"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA760</v>
-      </c>
-      <c r="B60" s="16" t="s">
+      <c r="C64" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="D64" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D60" s="16"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA764</v>
-      </c>
-      <c r="B61" s="16" t="s">
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA774</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" s="18" t="str">
+        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A104)-HEX2DEC(A65)-8,"]")</f>
+        <v>ldrh r2, [pc, #148]</v>
+      </c>
+      <c r="D65" s="18"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA778</v>
+      </c>
+      <c r="B66" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C66" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D61" s="16"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA768</v>
-      </c>
-      <c r="B62" s="16" t="s">
+      <c r="D66" s="18"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA77C</v>
+      </c>
+      <c r="B67" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C67" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D62" s="16"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA76C</v>
-      </c>
-      <c r="B63" s="16" t="s">
+      <c r="D67" s="18"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA780</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C68" s="18" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E68)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x00089C6C</v>
+      </c>
+      <c r="D68" s="18"/>
+      <c r="E68" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C63" s="16" t="s">
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA784</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D69" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="D63" s="16"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA770</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D64" s="16"/>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA774</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="C65" s="16" t="s">
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA788</v>
+      </c>
+      <c r="B70" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="16"/>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA778</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D66" s="17" t="s">
+      <c r="C70" s="20" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA77C</v>
-      </c>
-      <c r="B67" s="17" t="s">
+      <c r="D70" s="20"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA78C</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C71" s="20" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E71)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x0007F804</v>
+      </c>
+      <c r="D71" s="20"/>
+      <c r="E71" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C67" s="17" t="s">
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA790</v>
+      </c>
+      <c r="B72" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D67" s="17"/>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA780</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68" s="17"/>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA784</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C69" s="17" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E69)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x000876F8</v>
-      </c>
-      <c r="D69" s="17"/>
-      <c r="E69" s="2" t="s">
+      <c r="C72" s="22" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA788</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D70" s="17"/>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA78C</v>
-      </c>
-      <c r="B71" s="18" t="s">
+      <c r="D72" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C71" s="18" t="s">
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA794</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" s="22"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA798</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D74" s="22"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="24" t="str">
+        <f t="shared" ref="A75:A103" si="2">DEC2HEX(HEX2DEC(A74)+4,8)</f>
+        <v>000DA79C</v>
+      </c>
+      <c r="B75" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA790</v>
-      </c>
-      <c r="B72" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C72" s="18" t="str">
-        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A111)-HEX2DEC(A72)-8,"]")</f>
-        <v>ldrh r2, [pc, #148]</v>
-      </c>
-      <c r="D72" s="18"/>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA794</v>
-      </c>
-      <c r="B73" s="18" t="s">
+    <row r="76" spans="1:5">
+      <c r="A76" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA7A0</v>
+      </c>
+      <c r="B76" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" s="24"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA7A4</v>
+      </c>
+      <c r="B77" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C77" s="24" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E77)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x0007CCF4</v>
+      </c>
+      <c r="D77" s="24"/>
+      <c r="E77" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C73" s="18" t="s">
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA7A8</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D78" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="D73" s="18"/>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA798</v>
-      </c>
-      <c r="B74" s="19" t="s">
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA7AC</v>
+      </c>
+      <c r="B79" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C79" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="18"/>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA79C</v>
-      </c>
-      <c r="B75" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C75" s="18" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E75)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x00089C6C</v>
-      </c>
-      <c r="D75" s="18"/>
-      <c r="E75" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA7A0</v>
-      </c>
-      <c r="B76" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C76" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" s="20" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA7A4</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C77" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D77" s="20"/>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA7A8</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="C78" s="20" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E78)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x0007F804</v>
-      </c>
-      <c r="D78" s="20"/>
-      <c r="E78" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA7AC</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C79" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="D79" s="22" t="s">
-        <v>133</v>
-      </c>
+      <c r="D79" s="25"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="22" t="str">
-        <f t="shared" si="1"/>
+      <c r="A80" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>000DA7B0</v>
       </c>
-      <c r="B80" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="C80" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D80" s="22"/>
+      <c r="B80" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C80" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D80" s="25"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="22" t="str">
-        <f t="shared" ref="A81:A112" si="2">DEC2HEX(HEX2DEC(A80)+4,8)</f>
+      <c r="A81" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>000DA7B4</v>
       </c>
-      <c r="B81" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="D81" s="22"/>
+      <c r="B81" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="25"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="24" t="str">
+      <c r="A82" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7B8</v>
       </c>
-      <c r="B82" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D82" s="24" t="s">
-        <v>135</v>
+      <c r="B82" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="24" t="str">
+      <c r="A83" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7BC</v>
       </c>
-      <c r="B83" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C83" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D83" s="24"/>
+      <c r="B83" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C83" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D83" s="26"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="24" t="str">
+      <c r="A84" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7C0</v>
       </c>
-      <c r="B84" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="C84" s="24" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E84)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x0007CCF4</v>
-      </c>
-      <c r="D84" s="24"/>
-      <c r="E84" s="2" t="s">
-        <v>136</v>
-      </c>
+      <c r="B84" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D84" s="26"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="25" t="str">
+      <c r="A85" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7C4</v>
       </c>
-      <c r="B85" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>137</v>
-      </c>
+      <c r="B85" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C85" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" s="26"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="25" t="str">
+      <c r="A86" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7C8</v>
       </c>
-      <c r="B86" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="D86" s="25"/>
+      <c r="B86" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C86" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D86" s="26"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="25" t="str">
+      <c r="A87" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7CC</v>
       </c>
-      <c r="B87" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D87" s="25"/>
+      <c r="B87" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C87" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D87" s="26"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="25" t="str">
+      <c r="A88" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7D0</v>
       </c>
-      <c r="B88" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="C88" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D88" s="25"/>
+      <c r="B88" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D88" s="26"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="26" t="str">
@@ -2355,14 +2322,12 @@
         <v>000DA7D4</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D89" s="26" t="s">
         <v>140</v>
       </c>
+      <c r="D89" s="26"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="26" t="str">
@@ -2370,10 +2335,10 @@
         <v>000DA7D8</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="D90" s="26"/>
     </row>
@@ -2383,10 +2348,10 @@
         <v>000DA7DC</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="D91" s="26"/>
     </row>
@@ -2396,778 +2361,435 @@
         <v>000DA7E0</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="C92" s="26" t="s">
-        <v>146</v>
+        <v>186</v>
+      </c>
+      <c r="C92" s="26" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E92)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x00092ABC</v>
       </c>
       <c r="D92" s="26"/>
+      <c r="E92" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="26" t="str">
+      <c r="A93" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA7E4</v>
       </c>
-      <c r="B93" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="C93" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="D93" s="26"/>
+      <c r="B93" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="26" t="str">
+      <c r="A94" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA7E8</v>
       </c>
-      <c r="B94" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C94" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="D94" s="26"/>
+      <c r="B94" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="26" t="str">
+      <c r="A95" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA7EC</v>
       </c>
-      <c r="B95" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="C95" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="D95" s="26"/>
+      <c r="B95" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="26" t="str">
+      <c r="A96" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA7F0</v>
       </c>
-      <c r="B96" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C96" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="D96" s="26"/>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="26" t="str">
+      <c r="B96" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA7F4</v>
       </c>
-      <c r="B97" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C97" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D97" s="26"/>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="26" t="str">
+      <c r="B97" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA7F8</v>
       </c>
-      <c r="B98" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C98" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D98" s="26"/>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="26" t="str">
+      <c r="B98" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA7FC</v>
       </c>
-      <c r="B99" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C99" s="26" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E99)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x00092ABC</v>
-      </c>
-      <c r="D99" s="26"/>
-      <c r="E99" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="B99" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA800</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>156</v>
+      <c r="B100" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA804</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>155</v>
+      </c>
+      <c r="C101" s="2" t="str">
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r4, r5, r6, r7, r8, r9, lr}</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA808</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103" s="2" t="str">
         <f t="shared" si="2"/>
         <v>000DA80C</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>157</v>
+      </c>
+      <c r="C103" s="2" t="str">
+        <f>SUBSTITUTE(C101,"lr","pc")</f>
+        <v>pop {r4, r5, r6, r7, r8, r9, pc}</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A74:A104" si="3">DEC2HEX(HEX2DEC(A103)+4,8)</f>
         <v>000DA810</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA814</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA818</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA81C</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA820</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C108" s="2" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r4, r5, r6, r7, r8, r9, lr}</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA824</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA828</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C110" s="2" t="str">
-        <f>SUBSTITUTE(C108,"lr","pc")</f>
-        <v>pop {r4, r5, r6, r7, r8, r9, pc}</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA82C</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA830</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B115" s="2" t="str">
-        <f>RIGHT(E115,2)&amp;LEFT(E115,2)</f>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="1"/>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="C107" s="6"/>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="C108" s="6"/>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="C109" s="6"/>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="C110" s="6"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="C111" s="6"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="C112" s="6"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B166" s="2" t="str">
+        <f>RIGHT(E166,2)&amp;LEFT(E166,2)</f>
         <v>CC01</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D115" s="2">
+      <c r="C166" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D166" s="2">
         <v>460</v>
       </c>
-      <c r="E115" s="2" t="str">
-        <f>DEC2HEX(D115,4)</f>
+      <c r="E166" s="2" t="str">
+        <f>DEC2HEX(D166,4)</f>
         <v>01CC</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A115)+2,8)</f>
+    <row r="167" spans="1:5">
+      <c r="A167" s="2" t="str">
+        <f>DEC2HEX(HEX2DEC(A166)+2,8)</f>
         <v>0014AF42</v>
       </c>
-      <c r="B116" s="2" t="str">
-        <f t="shared" ref="B116:B130" si="3">RIGHT(E116,2)&amp;LEFT(E116,2)</f>
+      <c r="B167" s="2" t="str">
+        <f t="shared" ref="B167:B181" si="4">RIGHT(E167,2)&amp;LEFT(E167,2)</f>
         <v>6201</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D116" s="2">
+      <c r="C167" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D167" s="2">
         <v>354</v>
       </c>
-      <c r="E116" s="2" t="str">
-        <f t="shared" ref="E116:E130" si="4">DEC2HEX(D116,4)</f>
+      <c r="E167" s="2" t="str">
+        <f t="shared" ref="E167:E181" si="5">DEC2HEX(D167,4)</f>
         <v>0162</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="2" t="str">
-        <f t="shared" ref="A117:A130" si="5">DEC2HEX(HEX2DEC(A116)+2,8)</f>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2" t="str">
+        <f t="shared" ref="A168:A181" si="6">DEC2HEX(HEX2DEC(A167)+2,8)</f>
         <v>0014AF44</v>
       </c>
-      <c r="B117" s="2" t="str">
-        <f t="shared" si="3"/>
+      <c r="B168" s="2" t="str">
+        <f t="shared" si="4"/>
         <v>2F01</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D117" s="2">
+      <c r="C168" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D168" s="2">
         <v>303</v>
       </c>
-      <c r="E117" s="2" t="str">
+      <c r="E168" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>012F</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF46</v>
+      </c>
+      <c r="B169" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>012F</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="2" t="str">
+        <v>3601</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169" s="2">
+        <v>310</v>
+      </c>
+      <c r="E169" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF46</v>
-      </c>
-      <c r="B118" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>3601</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D118" s="2">
-        <v>310</v>
-      </c>
-      <c r="E118" s="2" t="str">
-        <f t="shared" si="4"/>
         <v>0136</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="2" t="str">
-        <f t="shared" si="5"/>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2" t="str">
+        <f t="shared" si="6"/>
         <v>0014AF48</v>
       </c>
-      <c r="B119" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>4E01</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D119" s="2">
-        <v>334</v>
-      </c>
-      <c r="E119" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>014E</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF4A</v>
-      </c>
-      <c r="B120" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>B500</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D120" s="2">
-        <v>181</v>
-      </c>
-      <c r="E120" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>00B5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0014AF4C</v>
-      </c>
-      <c r="B121" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-      <c r="E121" s="2" t="str">
+      <c r="B170" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="2" t="str">
+      <c r="C170" s="6"/>
+      <c r="E170" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF4E</v>
-      </c>
-      <c r="B122" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E122" s="2" t="str">
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF4A</v>
+      </c>
+      <c r="B171" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="2" t="str">
+      <c r="C171" s="6"/>
+      <c r="E171" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF50</v>
-      </c>
-      <c r="B123" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E123" s="2" t="str">
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF4C</v>
+      </c>
+      <c r="B172" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="2" t="str">
+      <c r="E172" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF52</v>
-      </c>
-      <c r="B124" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E124" s="2" t="str">
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF4E</v>
+      </c>
+      <c r="B173" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="2" t="str">
+      <c r="E173" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF54</v>
-      </c>
-      <c r="B125" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E125" s="2" t="str">
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF50</v>
+      </c>
+      <c r="B174" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="2" t="str">
+      <c r="E174" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF56</v>
-      </c>
-      <c r="B126" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E126" s="2" t="str">
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF52</v>
+      </c>
+      <c r="B175" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="2" t="str">
+      <c r="E175" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF58</v>
-      </c>
-      <c r="B127" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E127" s="2" t="str">
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF54</v>
+      </c>
+      <c r="B176" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="2" t="str">
+      <c r="E176" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF5A</v>
-      </c>
-      <c r="B128" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E128" s="2" t="str">
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF56</v>
+      </c>
+      <c r="B177" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="2" t="str">
+      <c r="E177" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF5C</v>
-      </c>
-      <c r="B129" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E129" s="2" t="str">
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF58</v>
+      </c>
+      <c r="B178" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="2" t="str">
+      <c r="E178" s="2" t="str">
         <f t="shared" si="5"/>
-        <v>0014AF5E</v>
-      </c>
-      <c r="B130" s="2" t="str">
-        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-      <c r="E130" s="2" t="str">
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v>0014AF5A</v>
+      </c>
+      <c r="B179" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B174" s="2" t="str">
-        <f>RIGHT(E174,2)&amp;LEFT(E174,2)</f>
-        <v>CC01</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D174" s="2">
-        <v>460</v>
-      </c>
-      <c r="E174" s="2" t="str">
-        <f>DEC2HEX(D174,4)</f>
-        <v>01CC</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A174)+2,8)</f>
-        <v>0014AF42</v>
-      </c>
-      <c r="B175" s="2" t="str">
-        <f t="shared" ref="B175:B189" si="6">RIGHT(E175,2)&amp;LEFT(E175,2)</f>
-        <v>6201</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D175" s="2">
-        <v>354</v>
-      </c>
-      <c r="E175" s="2" t="str">
-        <f t="shared" ref="E175:E189" si="7">DEC2HEX(D175,4)</f>
-        <v>0162</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="2" t="str">
-        <f t="shared" ref="A176:A189" si="8">DEC2HEX(HEX2DEC(A175)+2,8)</f>
-        <v>0014AF44</v>
-      </c>
-      <c r="B176" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>2F01</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D176" s="2">
-        <v>303</v>
-      </c>
-      <c r="E176" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>012F</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF46</v>
-      </c>
-      <c r="B177" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>3601</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D177" s="2">
-        <v>310</v>
-      </c>
-      <c r="E177" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0136</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF48</v>
-      </c>
-      <c r="B178" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="C178" s="6"/>
-      <c r="E178" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF4A</v>
-      </c>
-      <c r="B179" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="C179" s="6"/>
       <c r="E179" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0000</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF4C</v>
+        <f t="shared" si="6"/>
+        <v>0014AF5C</v>
       </c>
       <c r="B180" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0000</v>
       </c>
       <c r="E180" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0000</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF4E</v>
+        <f t="shared" si="6"/>
+        <v>0014AF5E</v>
       </c>
       <c r="B181" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0000</v>
       </c>
       <c r="E181" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF50</v>
-      </c>
-      <c r="B182" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E182" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF52</v>
-      </c>
-      <c r="B183" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E183" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF54</v>
-      </c>
-      <c r="B184" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E184" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF56</v>
-      </c>
-      <c r="B185" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E185" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF58</v>
-      </c>
-      <c r="B186" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E186" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF5A</v>
-      </c>
-      <c r="B187" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E187" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF5C</v>
-      </c>
-      <c r="B188" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E188" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>0014AF5E</v>
-      </c>
-      <c r="B189" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0000</v>
-      </c>
-      <c r="E189" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0000</v>
       </c>
     </row>

--- a/ARM Functions/Item Edits/Mega Stone Emergency Exit.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Emergency Exit.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F4927-B8C1-4D3D-A330-DBCE4B9896B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930039EB-892D-46A4-A3C6-BA2C528C4451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="188">
   <si>
     <t>mov r0, r5</t>
   </si>
@@ -207,9 +207,6 @@
     <t>check if current HP 0</t>
   </si>
   <si>
-    <t>bl 0x000938E8</t>
-  </si>
-  <si>
     <t>0E10A0E3</t>
   </si>
   <si>
@@ -546,9 +543,6 @@
     <t>F4DEFEEB</t>
   </si>
   <si>
-    <t>4A00001A</t>
-  </si>
-  <si>
     <t>4100008A</t>
   </si>
   <si>
@@ -567,61 +561,67 @@
     <t>cmp r0, 0x1</t>
   </si>
   <si>
-    <t>5400001A</t>
-  </si>
-  <si>
-    <t>33F2FFEB</t>
-  </si>
-  <si>
     <t>010050E3</t>
   </si>
   <si>
-    <t>4E00001A</t>
-  </si>
-  <si>
-    <t>83E4FEEB</t>
-  </si>
-  <si>
-    <t>CEDFFEEB</t>
-  </si>
-  <si>
-    <t>CADFFEEB</t>
-  </si>
-  <si>
-    <t>AA94FEEB</t>
-  </si>
-  <si>
-    <t>8EC3FEEB</t>
-  </si>
-  <si>
-    <t>EEB3FEEB</t>
-  </si>
-  <si>
-    <t>6589FEEB</t>
-  </si>
-  <si>
-    <t>E2B3FEEB</t>
-  </si>
-  <si>
-    <t>39BDFEEB</t>
-  </si>
-  <si>
-    <t>1C94FEEB</t>
-  </si>
-  <si>
-    <t>1994FEEB</t>
-  </si>
-  <si>
-    <t>5289FEEB</t>
-  </si>
-  <si>
-    <t>CFB3FEEB</t>
-  </si>
-  <si>
-    <t>B5E0FEEB</t>
-  </si>
-  <si>
-    <t>3989FEEA</t>
+    <t>bl 0x000611C0</t>
+  </si>
+  <si>
+    <t>5600001A</t>
+  </si>
+  <si>
+    <t>32F2FFEB</t>
+  </si>
+  <si>
+    <t>4F00001A</t>
+  </si>
+  <si>
+    <t>B71AFEEB</t>
+  </si>
+  <si>
+    <t>4A00000A</t>
+  </si>
+  <si>
+    <t>CCDFFEEB</t>
+  </si>
+  <si>
+    <t>C8DFFEEB</t>
+  </si>
+  <si>
+    <t>A894FEEB</t>
+  </si>
+  <si>
+    <t>8CC3FEEB</t>
+  </si>
+  <si>
+    <t>ECB3FEEB</t>
+  </si>
+  <si>
+    <t>6389FEEB</t>
+  </si>
+  <si>
+    <t>E0B3FEEB</t>
+  </si>
+  <si>
+    <t>37BDFEEB</t>
+  </si>
+  <si>
+    <t>1A94FEEB</t>
+  </si>
+  <si>
+    <t>1794FEEB</t>
+  </si>
+  <si>
+    <t>5089FEEB</t>
+  </si>
+  <si>
+    <t>CDB3FEEB</t>
+  </si>
+  <si>
+    <t>B3E0FEEB</t>
+  </si>
+  <si>
+    <t>3789FEEA</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1227,12 +1227,12 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="str">
-        <f t="shared" ref="A11:A74" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
+        <f t="shared" ref="A11:A76" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
         <v>000DA69C</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1298,7 +1298,7 @@
         <v>000DA6AC</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>17</v>
@@ -1327,8 +1327,8 @@
         <v>169</v>
       </c>
       <c r="C17" s="4" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A103)</f>
-        <v>bne 0x000DA80C</v>
+        <f>_xlfn.CONCAT("bne 0x",A105)</f>
+        <v>bne 0x000DA814</v>
       </c>
       <c r="D17" s="4"/>
     </row>
@@ -1366,7 +1366,7 @@
         <v>000DA6C0</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>18</v>
@@ -1374,18 +1374,18 @@
       <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2" t="str">
+      <c r="A21" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000DA6C4</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>166</v>
+      <c r="B21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1393,11 +1393,14 @@
         <f t="shared" si="1"/>
         <v>000DA6C8</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>171</v>
+      <c r="B22" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1405,27 +1408,24 @@
         <f t="shared" si="1"/>
         <v>000DA6CC</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A103)</f>
-        <v>bne 0x000DA80C</v>
+      <c r="B23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="8" t="str">
+      <c r="A24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DA6D0</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>48</v>
+      <c r="B24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A105)</f>
+        <v>bne 0x000DA814</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1434,10 +1434,10 @@
         <v>000DA6D4</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="3"/>
@@ -1447,13 +1447,14 @@
         <f t="shared" si="1"/>
         <v>000DA6D8</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>20</v>
+      <c r="B26" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D26" s="8"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="8" t="str">
@@ -1461,41 +1462,40 @@
         <v>000DA6DC</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C27" s="8" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A103)</f>
-        <v>bne 0x000DA80C</v>
+        <v>172</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>168</v>
       </c>
       <c r="D27" s="8"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="10" t="str">
+      <c r="A28" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DA6E0</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="B28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="10" t="str">
+      <c r="A29" s="8" t="str">
         <f t="shared" si="1"/>
         <v>000DA6E4</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="10"/>
+      <c r="B29" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="8" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A105)</f>
+        <v>beq 0x000DA814</v>
+      </c>
+      <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="10" t="str">
@@ -1503,12 +1503,14 @@
         <v>000DA6E8</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="10" t="str">
@@ -1516,10 +1518,10 @@
         <v>000DA6EC</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D31" s="10"/>
     </row>
@@ -1529,10 +1531,10 @@
         <v>000DA6F0</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D32" s="10"/>
     </row>
@@ -1542,10 +1544,10 @@
         <v>000DA6F4</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D33" s="10"/>
     </row>
@@ -1555,44 +1557,39 @@
         <v>000DA6F8</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>175</v>
+        <v>57</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>60</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D34" s="10"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="10" t="str">
         <f t="shared" si="1"/>
         <v>000DA6FC</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>61</v>
+      <c r="B35" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>63</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="10" t="str">
         <f t="shared" si="1"/>
         <v>000DA700</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="C36" s="10" t="str">
-        <f>_xlfn.CONCAT("bhi 0x",A103)</f>
-        <v>bhi 0x000DA80C</v>
+      <c r="B36" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1601,41 +1598,44 @@
         <v>000DA704</v>
       </c>
       <c r="B37" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA708</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="10" t="str">
+        <f>_xlfn.CONCAT("bhi 0x",A105)</f>
+        <v>bhi 0x000DA814</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA70C</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="D39" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA708</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="12"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA70C</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1644,85 +1644,81 @@
         <v>000DA710</v>
       </c>
       <c r="B40" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA714</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA718</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D40" s="12"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA714</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA718</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="13"/>
+      <c r="C42" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="12"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="13" t="str">
         <f t="shared" si="1"/>
         <v>000DA71C</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA720</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="13"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA724</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="13"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA720</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA724</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="C45" s="15" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E45)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x0008B564</v>
-      </c>
-      <c r="D45" s="15"/>
-      <c r="E45" s="2">
-        <v>768564</v>
-      </c>
+      <c r="D45" s="13"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="15" t="str">
@@ -1730,40 +1726,44 @@
         <v>000DA728</v>
       </c>
       <c r="B46" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA72C</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C47" s="15" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E47)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x0008B564</v>
+      </c>
+      <c r="D47" s="15"/>
+      <c r="E47" s="2">
+        <v>768564</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA730</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C46" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="15"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA72C</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA730</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D48" s="16"/>
+      <c r="D48" s="15"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="16" t="str">
@@ -1771,12 +1771,14 @@
         <v>000DA734</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="16"/>
+        <v>82</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="16" t="str">
@@ -1784,10 +1786,10 @@
         <v>000DA738</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D50" s="16"/>
     </row>
@@ -1797,10 +1799,10 @@
         <v>000DA73C</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="D51" s="16"/>
     </row>
@@ -1810,10 +1812,10 @@
         <v>000DA740</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D52" s="16"/>
     </row>
@@ -1823,10 +1825,10 @@
         <v>000DA744</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D53" s="16"/>
     </row>
@@ -1836,10 +1838,10 @@
         <v>000DA748</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D54" s="16"/>
     </row>
@@ -1849,10 +1851,10 @@
         <v>000DA74C</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D55" s="16"/>
     </row>
@@ -1862,10 +1864,10 @@
         <v>000DA750</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D56" s="16"/>
     </row>
@@ -1875,10 +1877,10 @@
         <v>000DA754</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="D57" s="16"/>
     </row>
@@ -1888,40 +1890,38 @@
         <v>000DA758</v>
       </c>
       <c r="B58" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="16"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA75C</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" s="16"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA760</v>
+      </c>
+      <c r="B60" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D58" s="16"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA75C</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="17" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA760</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D60" s="17"/>
+      <c r="C60" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D60" s="16"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="17" t="str">
@@ -1929,12 +1929,14 @@
         <v>000DA764</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D61" s="17"/>
+        <v>82</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="17" t="str">
@@ -1942,16 +1944,12 @@
         <v>000DA768</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="C62" s="17" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E62)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x000876F8</v>
+        <v>101</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="D62" s="17"/>
-      <c r="E62" s="2" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="17" t="str">
@@ -1959,41 +1957,42 @@
         <v>000DA76C</v>
       </c>
       <c r="B63" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D63" s="17"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA770</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C64" s="17" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E64)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x000876F8</v>
+      </c>
+      <c r="D64" s="17"/>
+      <c r="E64" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA774</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C63" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" s="17"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA770</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA774</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C65" s="18" t="str">
-        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A104)-HEX2DEC(A65)-8,"]")</f>
-        <v>ldrh r2, [pc, #148]</v>
-      </c>
-      <c r="D65" s="18"/>
+      <c r="D65" s="17"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="18" t="str">
@@ -2001,23 +2000,26 @@
         <v>000DA778</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D66" s="18"/>
+        <v>105</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="18" t="str">
         <f t="shared" si="1"/>
         <v>000DA77C</v>
       </c>
-      <c r="B67" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>111</v>
+      <c r="B67" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" s="18" t="str">
+        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A106)-HEX2DEC(A67)-8,"]")</f>
+        <v>ldrh r2, [pc, #148]</v>
       </c>
       <c r="D67" s="18"/>
     </row>
@@ -2027,44 +2029,42 @@
         <v>000DA780</v>
       </c>
       <c r="B68" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="18"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA784</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="18"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="18" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA788</v>
+      </c>
+      <c r="B70" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="C68" s="18" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E68)-HEX2DEC("6dd000"),8))</f>
+      <c r="C70" s="18" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E70)-HEX2DEC("6dd000"),8))</f>
         <v>bl 0x00089C6C</v>
       </c>
-      <c r="D68" s="18"/>
-      <c r="E68" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA784</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA788</v>
-      </c>
-      <c r="B70" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D70" s="20"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="20" t="str">
@@ -2072,44 +2072,44 @@
         <v>000DA78C</v>
       </c>
       <c r="B71" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA790</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="20"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA794</v>
+      </c>
+      <c r="B73" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C71" s="20" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E71)-HEX2DEC("6dd000"),8))</f>
+      <c r="C73" s="20" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E73)-HEX2DEC("6dd000"),8))</f>
         <v>bl 0x0007F804</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA790</v>
-      </c>
-      <c r="B72" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C72" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>000DA794</v>
-      </c>
-      <c r="B73" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C73" s="22" t="s">
+      <c r="D73" s="20"/>
+      <c r="E73" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D73" s="22"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="22" t="str">
@@ -2117,85 +2117,85 @@
         <v>000DA798</v>
       </c>
       <c r="B74" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA79C</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" s="22"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>000DA7A0</v>
+      </c>
+      <c r="B76" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="C74" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D74" s="22"/>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="24" t="str">
-        <f t="shared" ref="A75:A103" si="2">DEC2HEX(HEX2DEC(A74)+4,8)</f>
-        <v>000DA79C</v>
-      </c>
-      <c r="B75" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>000DA7A0</v>
-      </c>
-      <c r="B76" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D76" s="24"/>
+      <c r="C76" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D76" s="22"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A77:A106" si="2">DEC2HEX(HEX2DEC(A76)+4,8)</f>
         <v>000DA7A4</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C77" s="24" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E77)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x0007CCF4</v>
-      </c>
-      <c r="D77" s="24"/>
-      <c r="E77" s="2" t="s">
-        <v>122</v>
+        <v>3</v>
+      </c>
+      <c r="C77" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="25" t="str">
+      <c r="A78" s="24" t="str">
         <f t="shared" si="2"/>
         <v>000DA7A8</v>
       </c>
-      <c r="B78" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>123</v>
-      </c>
+      <c r="B78" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D78" s="24"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="25" t="str">
+      <c r="A79" s="24" t="str">
         <f t="shared" si="2"/>
         <v>000DA7AC</v>
       </c>
-      <c r="B79" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="D79" s="25"/>
+      <c r="B79" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C79" s="24" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E79)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x0007CCF4</v>
+      </c>
+      <c r="D79" s="24"/>
+      <c r="E79" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="25" t="str">
@@ -2203,12 +2203,14 @@
         <v>000DA7B0</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D80" s="25"/>
+        <v>82</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="25" t="str">
@@ -2216,40 +2218,38 @@
         <v>000DA7B4</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="D81" s="25"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="26" t="str">
+      <c r="A82" s="25" t="str">
         <f t="shared" si="2"/>
         <v>000DA7B8</v>
       </c>
-      <c r="B82" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C82" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D82" s="26" t="s">
-        <v>126</v>
-      </c>
+      <c r="B82" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" s="25"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="26" t="str">
+      <c r="A83" s="25" t="str">
         <f t="shared" si="2"/>
         <v>000DA7BC</v>
       </c>
-      <c r="B83" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="C83" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D83" s="26"/>
+      <c r="B83" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D83" s="25"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="26" t="str">
@@ -2257,12 +2257,14 @@
         <v>000DA7C0</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="D84" s="26"/>
+        <v>56</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="26" t="str">
@@ -2270,10 +2272,10 @@
         <v>000DA7C4</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D85" s="26"/>
     </row>
@@ -2282,11 +2284,11 @@
         <f t="shared" si="2"/>
         <v>000DA7C8</v>
       </c>
-      <c r="B86" s="27" t="s">
-        <v>133</v>
+      <c r="B86" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D86" s="26"/>
     </row>
@@ -2296,10 +2298,10 @@
         <v>000DA7CC</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D87" s="26"/>
     </row>
@@ -2308,11 +2310,11 @@
         <f t="shared" si="2"/>
         <v>000DA7D0</v>
       </c>
-      <c r="B88" s="26" t="s">
-        <v>137</v>
+      <c r="B88" s="27" t="s">
+        <v>132</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D88" s="26"/>
     </row>
@@ -2322,10 +2324,10 @@
         <v>000DA7D4</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D89" s="26"/>
     </row>
@@ -2335,10 +2337,10 @@
         <v>000DA7D8</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="D90" s="26"/>
     </row>
@@ -2348,10 +2350,10 @@
         <v>000DA7DC</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="D91" s="26"/>
     </row>
@@ -2361,42 +2363,41 @@
         <v>000DA7E0</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="C92" s="26" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E92)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x00092ABC</v>
+        <v>42</v>
+      </c>
+      <c r="C92" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="D92" s="26"/>
-      <c r="E92" s="2" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="2" t="str">
+      <c r="A93" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7E4</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>144</v>
-      </c>
+      <c r="B93" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93" s="26"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="2" t="str">
+      <c r="A94" s="26" t="str">
         <f t="shared" si="2"/>
         <v>000DA7E8</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>146</v>
+      <c r="B94" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" s="26" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E94)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x00092ABC</v>
+      </c>
+      <c r="D94" s="26"/>
+      <c r="E94" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2404,11 +2405,14 @@
         <f t="shared" si="2"/>
         <v>000DA7EC</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>147</v>
+      <c r="B95" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2417,10 +2421,10 @@
         <v>000DA7F0</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2428,11 +2432,11 @@
         <f t="shared" si="2"/>
         <v>000DA7F4</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>151</v>
+      <c r="B97" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2440,11 +2444,11 @@
         <f t="shared" si="2"/>
         <v>000DA7F8</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>153</v>
+      <c r="B98" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2452,11 +2456,11 @@
         <f t="shared" si="2"/>
         <v>000DA7FC</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>3</v>
+      <c r="B99" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>2</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2464,11 +2468,11 @@
         <f t="shared" si="2"/>
         <v>000DA800</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>44</v>
+      <c r="B100" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2477,11 +2481,10 @@
         <v>000DA804</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C101" s="2" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r4, r5, r6, r7, r8, r9, lr}</v>
+        <v>3</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2490,10 +2493,10 @@
         <v>000DA808</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>187</v>
+        <v>44</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>156</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2502,30 +2505,49 @@
         <v>000DA80C</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C103" s="2" t="str">
-        <f>SUBSTITUTE(C101,"lr","pc")</f>
-        <v>pop {r4, r5, r6, r7, r8, r9, pc}</v>
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r4, r5, r6, r7, r8, r9, lr}</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="2" t="str">
-        <f t="shared" ref="A74:A104" si="3">DEC2HEX(HEX2DEC(A103)+4,8)</f>
+        <f t="shared" si="2"/>
         <v>000DA810</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>158</v>
+      <c r="B104" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA814</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C105" s="2" t="str">
+        <f>SUBSTITUTE(C103,"lr","pc")</f>
+        <v>pop {r4, r5, r6, r7, r8, r9, pc}</v>
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="1"/>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="C107" s="6"/>
+      <c r="A106" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>000DA818</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="C108" s="6"/>
+      <c r="A108" s="1"/>
     </row>
     <row r="109" spans="1:3">
       <c r="C109" s="6"/>
@@ -2539,257 +2561,263 @@
     <row r="112" spans="1:3">
       <c r="C112" s="6"/>
     </row>
-    <row r="165" spans="1:5">
-      <c r="A165" s="1" t="s">
+    <row r="113" spans="3:3">
+      <c r="C113" s="6"/>
+    </row>
+    <row r="114" spans="3:3">
+      <c r="C114" s="6"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
-      <c r="A166" s="2" t="s">
+    <row r="168" spans="1:5">
+      <c r="A168" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B166" s="2" t="str">
-        <f>RIGHT(E166,2)&amp;LEFT(E166,2)</f>
+      <c r="B168" s="2" t="str">
+        <f>RIGHT(E168,2)&amp;LEFT(E168,2)</f>
         <v>CC01</v>
       </c>
-      <c r="C166" s="6" t="s">
+      <c r="C168" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D168" s="2">
         <v>460</v>
       </c>
-      <c r="E166" s="2" t="str">
-        <f>DEC2HEX(D166,4)</f>
+      <c r="E168" s="2" t="str">
+        <f>DEC2HEX(D168,4)</f>
         <v>01CC</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
-      <c r="A167" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A166)+2,8)</f>
-        <v>0014AF42</v>
-      </c>
-      <c r="B167" s="2" t="str">
-        <f t="shared" ref="B167:B181" si="4">RIGHT(E167,2)&amp;LEFT(E167,2)</f>
-        <v>6201</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D167" s="2">
-        <v>354</v>
-      </c>
-      <c r="E167" s="2" t="str">
-        <f t="shared" ref="E167:E181" si="5">DEC2HEX(D167,4)</f>
-        <v>0162</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
-      <c r="A168" s="2" t="str">
-        <f t="shared" ref="A168:A181" si="6">DEC2HEX(HEX2DEC(A167)+2,8)</f>
-        <v>0014AF44</v>
-      </c>
-      <c r="B168" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>2F01</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D168" s="2">
-        <v>303</v>
-      </c>
-      <c r="E168" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>012F</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF46</v>
+        <f>DEC2HEX(HEX2DEC(A168)+2,8)</f>
+        <v>0014AF42</v>
       </c>
       <c r="B169" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>3601</v>
+        <f t="shared" ref="B169:B183" si="3">RIGHT(E169,2)&amp;LEFT(E169,2)</f>
+        <v>6201</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D169" s="2">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="E169" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>0136</v>
+        <f t="shared" ref="E169:E183" si="4">DEC2HEX(D169,4)</f>
+        <v>0162</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="A170:A183" si="5">DEC2HEX(HEX2DEC(A169)+2,8)</f>
+        <v>0014AF44</v>
+      </c>
+      <c r="B170" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>2F01</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D170" s="2">
+        <v>303</v>
+      </c>
+      <c r="E170" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>012F</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>0014AF46</v>
+      </c>
+      <c r="B171" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>3601</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D171" s="2">
+        <v>310</v>
+      </c>
+      <c r="E171" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>0136</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2" t="str">
+        <f t="shared" si="5"/>
         <v>0014AF48</v>
       </c>
-      <c r="B170" s="2" t="str">
+      <c r="B172" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>0000</v>
+      </c>
+      <c r="C172" s="6"/>
+      <c r="E172" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="C170" s="6"/>
-      <c r="E170" s="2" t="str">
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF4A</v>
+      </c>
+      <c r="B173" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="171" spans="1:5">
-      <c r="A171" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF4A</v>
-      </c>
-      <c r="B171" s="2" t="str">
+      <c r="C173" s="6"/>
+      <c r="E173" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="C171" s="6"/>
-      <c r="E171" s="2" t="str">
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF4C</v>
+      </c>
+      <c r="B174" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF4C</v>
-      </c>
-      <c r="B172" s="2" t="str">
+      <c r="E174" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E172" s="2" t="str">
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF4E</v>
+      </c>
+      <c r="B175" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF4E</v>
-      </c>
-      <c r="B173" s="2" t="str">
+      <c r="E175" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E173" s="2" t="str">
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF50</v>
+      </c>
+      <c r="B176" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF50</v>
-      </c>
-      <c r="B174" s="2" t="str">
+      <c r="E176" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E174" s="2" t="str">
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF52</v>
+      </c>
+      <c r="B177" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF52</v>
-      </c>
-      <c r="B175" s="2" t="str">
+      <c r="E177" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E175" s="2" t="str">
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF54</v>
+      </c>
+      <c r="B178" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF54</v>
-      </c>
-      <c r="B176" s="2" t="str">
+      <c r="E178" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E176" s="2" t="str">
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF56</v>
+      </c>
+      <c r="B179" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF56</v>
-      </c>
-      <c r="B177" s="2" t="str">
+      <c r="E179" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E177" s="2" t="str">
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF58</v>
+      </c>
+      <c r="B180" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF58</v>
-      </c>
-      <c r="B178" s="2" t="str">
+      <c r="E180" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E178" s="2" t="str">
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF5A</v>
+      </c>
+      <c r="B181" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF5A</v>
-      </c>
-      <c r="B179" s="2" t="str">
+      <c r="E181" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E179" s="2" t="str">
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF5C</v>
+      </c>
+      <c r="B182" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF5C</v>
-      </c>
-      <c r="B180" s="2" t="str">
+      <c r="E182" s="2" t="str">
         <f t="shared" si="4"/>
         <v>0000</v>
       </c>
-      <c r="E180" s="2" t="str">
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="2" t="str">
         <f t="shared" si="5"/>
+        <v>0014AF5E</v>
+      </c>
+      <c r="B183" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>0000</v>
       </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>0014AF5E</v>
-      </c>
-      <c r="B181" s="2" t="str">
+      <c r="E183" s="2" t="str">
         <f t="shared" si="4"/>
-        <v>0000</v>
-      </c>
-      <c r="E181" s="2" t="str">
-        <f t="shared" si="5"/>
         <v>0000</v>
       </c>
     </row>
